--- a/ci-cd-merge-resolver/repoCollector/datasets/antlr4.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/antlr4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,42 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>a9dc3ebd86ea737fb9210b0a9f8e6ab45c592560</t>
+  </si>
+  <si>
+    <t>428ff28f354cb6da8acbe623aec989f757e9bd83</t>
+  </si>
+  <si>
+    <t>fed8c97bda1a80ce62828c25083a45e8070d7108</t>
+  </si>
+  <si>
+    <t>f8e7a2cf089f8bb3e3b8384361ac96f81bdad2c2</t>
+  </si>
+  <si>
+    <t>628aa8ff02a1d2cff673ce28ca3da6114112eba8</t>
+  </si>
+  <si>
+    <t>e967463e9110b669a56f2c5e6f3fe7ce4434e703</t>
+  </si>
+  <si>
+    <t>eaed562cb30658057109d1aa6bf11961b4c3d0de</t>
+  </si>
+  <si>
+    <t>16242e43c02600a8509e63e848e43c1d2588fe48</t>
+  </si>
+  <si>
+    <t>b4c34da1f0e2fde321a18861a63ac88a671835cc</t>
+  </si>
+  <si>
+    <t>7832bb278df59c12948c58688eab2d10f5956940</t>
+  </si>
+  <si>
+    <t>a8d828016e54adfc403326d8e56d93e7c75c27fc</t>
+  </si>
+  <si>
+    <t>14938591d7dceba52457cf91b067d6de89025dc4</t>
+  </si>
+  <si>
     <t>ca2539a6a76ff48c63471a65a5cc98931c069e7d</t>
   </si>
   <si>
@@ -51,6 +87,15 @@
   </si>
   <si>
     <t>6a2cd79aa9ce049e074b3a7d26f40dc13cb5897e</t>
+  </si>
+  <si>
+    <t>ccad5bd9bcb8bd3df866d0d89ea4040b23beca77</t>
+  </si>
+  <si>
+    <t>253cd172a442d60fef2df2f7d7f72ef140bb7d03</t>
+  </si>
+  <si>
+    <t>08e9776a4ac507d931e8f3e282b2778cd7640af0</t>
   </si>
 </sst>
 </file>
@@ -95,7 +140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,13 +186,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>118.0</v>
+        <v>4.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -156,10 +201,170 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>7.197999954223633</v>
+        <v>3.6640000343322754</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>3.4670000076293945</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>1.7740000486373901</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>1.4119999408721924</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>3617.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>73.66499328613281</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1959.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>699.1849365234375</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
